--- a/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2512403_PERMANENCIAFINAL_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2512403_PERMANENCIAFINAL_PROCESSED.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2633</v>
+        <v>4.5441</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7864</v>
+        <v>5.8202</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.5231</v>
+        <v>-1.2761</v>
       </c>
       <c r="G2" t="n">
-        <v>4.8623</v>
+        <v>4.8833</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7693</v>
+        <v>0.7708</v>
       </c>
       <c r="I2" t="n">
-        <v>4.093</v>
+        <v>4.1125</v>
       </c>
       <c r="J2" t="n">
-        <v>6.0583</v>
+        <v>6.1373</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1044</v>
+        <v>1.1445</v>
       </c>
       <c r="L2" t="n">
-        <v>4.9539</v>
+        <v>4.9929</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.196</v>
+        <v>-1.254</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3351</v>
+        <v>-0.3736</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.8609</v>
+        <v>-0.8804</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4097</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1893</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3539</v>
+        <v>0.2662</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5432</v>
+        <v>-0.2005</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.4227</v>
+        <v>1.4411</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.4227</v>
+        <v>-1.4411</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. TOLEDO ZAMORA</t>
+          <t>F. HERNANDEZ MARTINEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2504</v>
+        <v>4.1301</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7674</v>
+        <v>4.5575</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.5171</v>
+        <v>-0.4274</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4665</v>
+        <v>3.1518</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4824</v>
+        <v>0.3956</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9841</v>
+        <v>2.7561</v>
       </c>
       <c r="J3" t="n">
-        <v>2.761</v>
+        <v>3.6131</v>
       </c>
       <c r="K3" t="n">
-        <v>1.4029</v>
+        <v>0.9278</v>
       </c>
       <c r="L3" t="n">
-        <v>1.358</v>
+        <v>2.6853</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2944</v>
+        <v>-0.4614</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9205</v>
+        <v>-0.5322</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6261</v>
+        <v>0.0708</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R3" t="n">
-        <v>1.0242</v>
+        <v>1.6196</v>
       </c>
       <c r="S3" t="n">
-        <v>2.0259</v>
+        <v>0.2133</v>
       </c>
       <c r="T3" t="n">
-        <v>2.0178</v>
+        <v>0.0136</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0081</v>
+        <v>0.1997</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2421</v>
+        <v>0.1577</v>
       </c>
       <c r="W3" t="n">
-        <v>2.013</v>
+        <v>1.943</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.255</v>
+        <v>-1.7853</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F. HERNANDEZ MARTINEZ</t>
+          <t>H. KABASELE KASONGA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8641</v>
+        <v>3.7857</v>
       </c>
       <c r="E4" t="n">
-        <v>4.0592</v>
+        <v>1.7218</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1951</v>
+        <v>2.0639</v>
       </c>
       <c r="G4" t="n">
-        <v>3.109</v>
+        <v>2.3457</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4013</v>
+        <v>2.5297</v>
       </c>
       <c r="I4" t="n">
-        <v>2.7077</v>
+        <v>-0.184</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5195</v>
+        <v>2.651</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9035</v>
+        <v>2.5082</v>
       </c>
       <c r="L4" t="n">
-        <v>2.6161</v>
+        <v>0.1428</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4106</v>
+        <v>-0.3052</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5022</v>
+        <v>0.0215</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0916</v>
+        <v>-0.3267</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0047</v>
+        <v>0.2375</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3429</v>
+        <v>0.1763</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3476</v>
+        <v>0.0612</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1359</v>
+        <v>0.5951</v>
       </c>
       <c r="W4" t="n">
-        <v>1.9068</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.7709</v>
+        <v>0.6883</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H. KABASELE KASONGA</t>
+          <t>C. TOLEDO ZAMORA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.7752</v>
+        <v>3.5752</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4603</v>
+        <v>5.2811</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3148</v>
+        <v>-1.7059</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3494</v>
+        <v>2.4756</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5199</v>
+        <v>0.4936</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1705</v>
+        <v>1.982</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5977</v>
+        <v>2.835</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4647</v>
+        <v>1.4599</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1331</v>
+        <v>1.3752</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2483</v>
+        <v>-0.3595</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0552</v>
+        <v>-0.9663</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3035</v>
+        <v>0.6068</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6145</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6388</v>
+        <v>1.0123</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2209</v>
+        <v>1.3505</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.007</v>
+        <v>1.4221</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2279</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5903</v>
+        <v>-0.2509</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.1062</v>
+        <v>2.0362</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6965</v>
+        <v>-2.2872</v>
       </c>
     </row>
     <row r="6">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4859</v>
+        <v>0.9673</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0842</v>
+        <v>0.5662</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4016</v>
+        <v>0.401</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1271</v>
+        <v>0.1062</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.612</v>
+        <v>-2.6282</v>
       </c>
       <c r="I6" t="n">
-        <v>2.7391</v>
+        <v>2.7344</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0752</v>
+        <v>-0.0264</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.0259</v>
+        <v>-1.9979</v>
       </c>
       <c r="L6" t="n">
-        <v>1.9508</v>
+        <v>1.9715</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2023</v>
+        <v>0.1326</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.586</v>
+        <v>-0.6303</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7884</v>
+        <v>0.7629</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.6388</v>
+        <v>-1.6196</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.954</v>
+        <v>-0.4948</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2035</v>
+        <v>0.152</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7504999999999999</v>
+        <v>-0.6469</v>
       </c>
       <c r="V6" t="n">
-        <v>2.9515</v>
+        <v>2.9755</v>
       </c>
       <c r="W6" t="n">
-        <v>3.4356</v>
+        <v>3.4774</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.4841</v>
+        <v>-0.5019</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. MILADINOVIC</t>
+          <t>T. BOUNDI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2285</v>
+        <v>0.0567</v>
       </c>
       <c r="E7" t="n">
-        <v>0.232</v>
+        <v>0.0198</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0035</v>
+        <v>0.0369</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.0948</v>
+        <v>0.2375</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.3548</v>
+        <v>0.099</v>
       </c>
       <c r="I7" t="n">
-        <v>0.26</v>
+        <v>0.1384</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.2287</v>
+        <v>0.0198</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.769</v>
+        <v>0.0198</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.4597</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1339</v>
+        <v>0.2177</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5857</v>
+        <v>0.0793</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7197</v>
+        <v>0.1384</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4097</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0242</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6145</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2786</v>
+        <v>-0.1808</v>
       </c>
       <c r="T7" t="n">
-        <v>1.3043</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0257</v>
+        <v>-0.1808</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4544</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1806</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.7262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. BOUNDI</t>
+          <t>A. DUVAL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003</v>
+        <v>-0.5004999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0195</v>
+        <v>2.3515</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0165</v>
+        <v>-2.852</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2424</v>
+        <v>0.2234</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1031</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1394</v>
+        <v>0.1442</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0195</v>
+        <v>1.5542</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0195</v>
+        <v>0.9272</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.6271</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2229</v>
+        <v>-1.3309</v>
       </c>
       <c r="N8" t="n">
-        <v>0.08359999999999999</v>
+        <v>-0.848</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1394</v>
+        <v>-0.4829</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.2025</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.0123</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.2147</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2394</v>
+        <v>0.2639</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.3684</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2394</v>
+        <v>-0.1045</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.1902</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.4411</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-2.6313</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. CADME ARIAS</t>
+          <t>G. MILADINOVIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2197</v>
+        <v>-0.7179</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6607</v>
+        <v>-0.4862</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.2317</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.13</v>
+        <v>-1.1073</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.0718</v>
+        <v>-1.3635</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0582</v>
+        <v>0.2562</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.0227</v>
+        <v>-1.2056</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.0122</v>
+        <v>-0.752</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0105</v>
+        <v>-0.4536</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1073</v>
+        <v>0.0983</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0596</v>
+        <v>-0.6115</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0477</v>
+        <v>0.7098</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6145</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.0123</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8117</v>
+        <v>0.3569</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8779</v>
+        <v>0.5414</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-0.1845</v>
       </c>
       <c r="V9" t="n">
-        <v>0.4841</v>
+        <v>0.4374</v>
       </c>
       <c r="W9" t="n">
-        <v>0.4841</v>
+        <v>1.1902</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.7528</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>U. ZAMORA MANA</t>
+          <t>G. CADME ARIAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2439</v>
+        <v>-1.0571</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2463</v>
+        <v>-0.5816</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4903</v>
+        <v>-0.4755</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0207</v>
+        <v>-3.1435</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7946</v>
+        <v>-3.0831</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8153</v>
+        <v>-0.0604</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7048</v>
+        <v>-1.99</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5992</v>
+        <v>-1.9973</v>
       </c>
       <c r="L10" t="n">
-        <v>1.304</v>
+        <v>0.0072</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6841</v>
+        <v>-1.1535</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1954</v>
+        <v>-1.0859</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4887</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4097</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4097</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4937</v>
+        <v>0.9772</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4585</v>
+        <v>0.9065</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0352</v>
+        <v>0.0706</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.1806</v>
+        <v>0.5019</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.5019</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1806</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. MARTINEZ-QUINTANILLA JIMENEZ</t>
+          <t>U. ZAMORA MANA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4807</v>
+        <v>-1.156</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6072</v>
+        <v>0.478</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1265</v>
+        <v>-1.634</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.7951</v>
+        <v>0.0017</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4266</v>
+        <v>-0.8097</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.3685</v>
+        <v>0.8114</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.9522</v>
+        <v>0.7186</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6772</v>
+        <v>-0.5933</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.275</v>
+        <v>1.3119</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1571</v>
+        <v>-0.7169</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2507</v>
+        <v>-0.2164</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0935</v>
+        <v>-0.5006</v>
       </c>
       <c r="P11" t="n">
-        <v>1.0242</v>
+        <v>0.4049</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.0242</v>
+        <v>0.4049</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7099</v>
+        <v>-0.3724</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.655</v>
+        <v>-0.2406</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0549</v>
+        <v>-0.1318</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.1902</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. DUVAL</t>
+          <t>R. MARTINEZ-QUINTANILLA JIMENEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.4953</v>
+        <v>-1.5065</v>
       </c>
       <c r="E12" t="n">
-        <v>1.3038</v>
+        <v>-2.4738</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.7991</v>
+        <v>0.9673</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2118</v>
+        <v>-1.8024</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0808</v>
+        <v>-0.4345</v>
       </c>
       <c r="I12" t="n">
-        <v>0.131</v>
+        <v>-1.3679</v>
       </c>
       <c r="J12" t="n">
-        <v>1.4865</v>
+        <v>-1.9373</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8898</v>
+        <v>-0.6723</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5968</v>
+        <v>-1.2649</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.2747</v>
+        <v>0.1349</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8089</v>
+        <v>0.2379</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4658</v>
+        <v>-0.103</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2048</v>
+        <v>1.0123</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0242</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2291</v>
+        <v>1.0123</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7313</v>
+        <v>-0.7163</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5810999999999999</v>
+        <v>-0.5365</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1502</v>
+        <v>-0.1798</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.1806</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.4227</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.6033</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.4308</v>
+        <v>12.1211</v>
       </c>
       <c r="E13" t="n">
-        <v>15.6912</v>
+        <v>17.2545</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.2608</v>
+        <v>-5.1335</v>
       </c>
       <c r="G13" t="n">
-        <v>7.369300000000001</v>
+        <v>7.372</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.903</v>
+        <v>-3.951099999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>11.2724</v>
+        <v>11.3229</v>
       </c>
       <c r="J13" t="n">
-        <v>11.8685</v>
+        <v>12.3697</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7012999999999995</v>
+        <v>0.9745999999999996</v>
       </c>
       <c r="L13" t="n">
-        <v>11.1675</v>
+        <v>11.3954</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.4992</v>
+        <v>-4.9979</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.603899999999999</v>
+        <v>-4.9255</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1051000000000002</v>
+        <v>-0.07249999999999991</v>
       </c>
       <c r="P13" t="n">
-        <v>1.024</v>
+        <v>1.0125</v>
       </c>
       <c r="Q13" t="n">
-        <v>-10.2422</v>
+        <v>-10.1228</v>
       </c>
       <c r="R13" t="n">
-        <v>11.2665</v>
+        <v>11.135</v>
       </c>
       <c r="S13" t="n">
-        <v>1.0242</v>
+        <v>1.7007</v>
       </c>
       <c r="T13" t="n">
-        <v>2.305899999999999</v>
+        <v>3.069399999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.2817</v>
+        <v>-1.3688</v>
       </c>
       <c r="V13" t="n">
-        <v>2.012899999999999</v>
+        <v>2.0363</v>
       </c>
       <c r="W13" t="n">
-        <v>11.7593</v>
+        <v>11.9377</v>
       </c>
       <c r="X13" t="n">
-        <v>-9.7463</v>
+        <v>-9.901500000000002</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5399</v>
+        <v>2.5679</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6091</v>
+        <v>3.3985</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.0692</v>
+        <v>-0.8306</v>
       </c>
       <c r="G14" t="n">
-        <v>2.4772</v>
+        <v>2.5245</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1891</v>
+        <v>-0.1596</v>
       </c>
       <c r="I14" t="n">
-        <v>2.6662</v>
+        <v>2.6842</v>
       </c>
       <c r="J14" t="n">
-        <v>4.4225</v>
+        <v>4.5407</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2443</v>
+        <v>-0.1811</v>
       </c>
       <c r="L14" t="n">
-        <v>4.6668</v>
+        <v>4.7218</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.9454</v>
+        <v>-2.0162</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0552</v>
+        <v>0.0215</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.0006</v>
+        <v>-2.0376</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3917</v>
+        <v>-0.3941</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8264</v>
+        <v>-0.1785</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5653</v>
+        <v>-0.2156</v>
       </c>
       <c r="V14" t="n">
-        <v>0.4544</v>
+        <v>0.4374</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X14" t="n">
-        <v>0.2124</v>
+        <v>0.1865</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. TIKHONENKO ANDRIYASHCHENKO</t>
+          <t>J. SANTA BARBARA CARCELEN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.853</v>
+        <v>0.9957</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1959</v>
+        <v>3.7477</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0488</v>
+        <v>-2.752</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1413</v>
+        <v>-0.89</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.4348</v>
+        <v>3.3992</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5760999999999999</v>
+        <v>-4.2892</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4997</v>
+        <v>1.4469</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6577</v>
+        <v>2.9033</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1581</v>
+        <v>-1.4564</v>
       </c>
       <c r="M15" t="n">
-        <v>0.641</v>
+        <v>-2.3369</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2229</v>
+        <v>0.4959</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4181</v>
+        <v>-2.8327</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4097</v>
+        <v>1.0123</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4097</v>
+        <v>1.0123</v>
       </c>
       <c r="S15" t="n">
-        <v>0.302</v>
+        <v>-0.2924</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3038</v>
+        <v>0.0136</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0018</v>
+        <v>-0.306</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.1658</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.2872</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.1214</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. SANTA BARBARA CARCELEN</t>
+          <t>M. TIKHONENKO ANDRIYASHCHENKO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0365</v>
+        <v>0.6347</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9971</v>
+        <v>-0.6009</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.0335</v>
+        <v>1.2356</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8899</v>
+        <v>0.1394</v>
       </c>
       <c r="H16" t="n">
-        <v>3.3841</v>
+        <v>-0.4349</v>
       </c>
       <c r="I16" t="n">
-        <v>-4.2739</v>
+        <v>0.5743</v>
       </c>
       <c r="J16" t="n">
-        <v>1.372</v>
+        <v>-0.4936</v>
       </c>
       <c r="K16" t="n">
-        <v>2.855</v>
+        <v>-0.6526</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.483</v>
+        <v>0.159</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.2618</v>
+        <v>0.633</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5291</v>
+        <v>0.2177</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.7909</v>
+        <v>0.4153</v>
       </c>
       <c r="P16" t="n">
-        <v>1.0242</v>
+        <v>0.4049</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.0242</v>
+        <v>0.4049</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3149</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6299</v>
+        <v>-0.1074</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6850000000000001</v>
+        <v>0.1977</v>
       </c>
       <c r="V16" t="n">
-        <v>1.1441</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.255</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.385</v>
+        <v>-0.1465</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6002999999999999</v>
+        <v>-0.5767</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2153</v>
+        <v>0.4302</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0777</v>
+        <v>1.0801</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.5136</v>
+        <v>-1.5217</v>
       </c>
       <c r="I17" t="n">
-        <v>2.5914</v>
+        <v>2.6018</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9622</v>
+        <v>2.0159</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.095</v>
+        <v>-1.0688</v>
       </c>
       <c r="L17" t="n">
-        <v>3.0572</v>
+        <v>3.0846</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8844</v>
+        <v>-0.9358</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4186</v>
+        <v>-0.4529</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4658</v>
+        <v>-0.4829</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.3018</v>
+        <v>-4.2515</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0946</v>
+        <v>0.1137</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5588</v>
+        <v>0.4687</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6534</v>
+        <v>-0.355</v>
       </c>
       <c r="V17" t="n">
-        <v>1.7047</v>
+        <v>1.6964</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5241</v>
+        <v>0.5062</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4502</v>
+        <v>-0.4175</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6753</v>
+        <v>-0.5479000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2251</v>
+        <v>0.1303</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1263</v>
+        <v>0.1194</v>
       </c>
       <c r="H18" t="n">
-        <v>0.326</v>
+        <v>0.3167</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1997</v>
+        <v>-0.1973</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5982</v>
+        <v>-0.5928</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0195</v>
+        <v>0.0198</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6177</v>
+        <v>-0.6126</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7245</v>
+        <v>0.7122000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3065</v>
+        <v>0.297</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4181</v>
+        <v>0.4153</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1572</v>
+        <v>0.1999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3191</v>
+        <v>-0.206</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4763</v>
+        <v>0.4059</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9385</v>
+        <v>-0.9393</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6782</v>
+        <v>-0.8118</v>
       </c>
       <c r="E19" t="n">
-        <v>3.2155</v>
+        <v>3.1189</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.8937</v>
+        <v>-3.9307</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1811</v>
+        <v>-1.1743</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1558</v>
+        <v>-0.1392</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0253</v>
+        <v>-1.0351</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6559</v>
+        <v>0.7127</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6808999999999999</v>
+        <v>0.7289</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.025</v>
+        <v>-0.0163</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.837</v>
+        <v>-1.887</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8367</v>
+        <v>-0.8682</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0003</v>
+        <v>-1.0188</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="S19" t="n">
-        <v>0.056</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0809</v>
+        <v>-0.2736</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1369</v>
+        <v>0.1827</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="W19" t="n">
-        <v>2.8453</v>
+        <v>2.8823</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.6033</v>
+        <v>-2.6313</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1824</v>
+        <v>-1.1638</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9784</v>
+        <v>-0.9346</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.204</v>
+        <v>-0.2292</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.3782</v>
+        <v>-2.3777</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7998</v>
+        <v>0.7911</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.178</v>
+        <v>-3.1688</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.1595</v>
+        <v>-1.1248</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9953</v>
+        <v>1.0075</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.1548</v>
+        <v>-2.1323</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2186</v>
+        <v>-1.2529</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1954</v>
+        <v>-0.2164</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0232</v>
+        <v>-1.0365</v>
       </c>
       <c r="P20" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.103</v>
+        <v>-0.0697</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1811</v>
+        <v>0.1902</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2841</v>
+        <v>-0.2599</v>
       </c>
       <c r="V20" t="n">
-        <v>0.0696</v>
+        <v>0.0688</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.0696</v>
+        <v>0.0688</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.235</v>
+        <v>-1.1947</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3945</v>
+        <v>0.4046</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6295</v>
+        <v>-1.5993</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.09370000000000001</v>
+        <v>-0.1006</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2619</v>
+        <v>0.2572</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3556</v>
+        <v>-0.3578</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0785</v>
+        <v>0.0793</v>
       </c>
       <c r="K21" t="n">
-        <v>0.039</v>
+        <v>0.0395</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0395</v>
+        <v>0.0398</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1722</v>
+        <v>-0.1798</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2229</v>
+        <v>0.2177</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3952</v>
+        <v>-0.3975</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1656</v>
+        <v>-0.1064</v>
       </c>
       <c r="T21" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2394</v>
+        <v>-0.1808</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4227</v>
+        <v>-1.4411</v>
       </c>
     </row>
     <row r="22">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.384</v>
+        <v>-1.8114</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9633</v>
+        <v>-1.2462</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4206</v>
+        <v>-0.5652</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.6817</v>
+        <v>-1.7119</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2259</v>
+        <v>-0.2367</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.4558</v>
+        <v>-1.4753</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2156</v>
+        <v>0.2178</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1366</v>
+        <v>0.1383</v>
       </c>
       <c r="L22" t="n">
-        <v>0.079</v>
+        <v>0.0795</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.8973</v>
+        <v>-1.9297</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3625</v>
+        <v>-0.3749</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.5348</v>
+        <v>-1.5548</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R22" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="S22" t="n">
-        <v>1.4572</v>
+        <v>1.0464</v>
       </c>
       <c r="T22" t="n">
-        <v>0.8695000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5877</v>
+        <v>0.4859</v>
       </c>
       <c r="V22" t="n">
-        <v>0.0696</v>
+        <v>0.0688</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.0696</v>
+        <v>0.0688</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. MARTINEZ MEGIAS</t>
+          <t>C. FIELDS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.7193</v>
+        <v>-2.267</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.2601</v>
+        <v>1.7962</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.4592</v>
+        <v>-4.0632</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1355</v>
+        <v>-2.8669</v>
       </c>
       <c r="H23" t="n">
-        <v>1.352</v>
+        <v>1.2044</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.2166</v>
+        <v>-4.0713</v>
       </c>
       <c r="J23" t="n">
-        <v>1.4757</v>
+        <v>-1.466</v>
       </c>
       <c r="K23" t="n">
-        <v>1.4362</v>
+        <v>1.1036</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0395</v>
+        <v>-2.5696</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3402</v>
+        <v>-1.4009</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.08409999999999999</v>
+        <v>0.1008</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.2561</v>
+        <v>-1.5017</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.2291</v>
+        <v>-1.0123</v>
       </c>
       <c r="R23" t="n">
-        <v>0.8194</v>
+        <v>1.4172</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2198</v>
+        <v>-0.218</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8862</v>
+        <v>0.1087</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.106</v>
+        <v>-0.3267</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.2253</v>
+        <v>0.413</v>
       </c>
       <c r="W23" t="n">
-        <v>-1.393</v>
+        <v>4.1657</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.8324</v>
+        <v>-3.7527</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C. FIELDS</t>
+          <t>K. FELIZOR</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.8207</v>
+        <v>-3.1646</v>
       </c>
       <c r="E24" t="n">
-        <v>1.017</v>
+        <v>-2.5765</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.8377</v>
+        <v>-0.5881</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.8788</v>
+        <v>-2.2392</v>
       </c>
       <c r="H24" t="n">
-        <v>1.1767</v>
+        <v>-0.889</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.0555</v>
+        <v>-1.3502</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.5515</v>
+        <v>-1.8582</v>
       </c>
       <c r="K24" t="n">
-        <v>1.0379</v>
+        <v>-0.5933</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.5895</v>
+        <v>-1.2649</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.3273</v>
+        <v>-0.381</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1388</v>
+        <v>-0.2957</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.4661</v>
+        <v>-0.0853</v>
       </c>
       <c r="P24" t="n">
-        <v>0.4097</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.0242</v>
+        <v>-1.2147</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4339</v>
+        <v>1.2147</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7695</v>
+        <v>0.8599</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5393</v>
+        <v>0.4965</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2301</v>
+        <v>0.3635</v>
       </c>
       <c r="V24" t="n">
-        <v>0.4179</v>
+        <v>-1.7853</v>
       </c>
       <c r="W24" t="n">
-        <v>4.1321</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-3.7142</v>
+        <v>-1.7853</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>K. FELIZOR</t>
+          <t>J. MARTINEZ MEGIAS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.9323</v>
+        <v>-3.2694</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.2992</v>
+        <v>-0.8016</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.6331</v>
+        <v>-2.4678</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.2238</v>
+        <v>0.1252</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.8782</v>
+        <v>1.3634</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.3456</v>
+        <v>-1.2382</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.8741</v>
+        <v>1.52</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.5992</v>
+        <v>1.4803</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.275</v>
+        <v>0.0398</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.3496</v>
+        <v>-1.3949</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.279</v>
+        <v>-0.1169</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.0706</v>
+        <v>-1.278</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="R25" t="n">
-        <v>1.2291</v>
+        <v>0.8098</v>
       </c>
       <c r="S25" t="n">
-        <v>1.0624</v>
+        <v>-0.767</v>
       </c>
       <c r="T25" t="n">
-        <v>0.804</v>
+        <v>0.2698</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2584</v>
+        <v>-1.0367</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.7709</v>
+        <v>-2.2227</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>-1.3767</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.7709</v>
+        <v>-0.846</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-11.4307</v>
+        <v>-10.0484</v>
       </c>
       <c r="E26" t="n">
-        <v>4.260699999999999</v>
+        <v>5.181500000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-15.6913</v>
+        <v>-15.23</v>
       </c>
       <c r="G26" t="n">
-        <v>-7.369200000000001</v>
+        <v>-7.371999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>3.903100000000001</v>
+        <v>3.950899999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-11.2723</v>
+        <v>-11.3229</v>
       </c>
       <c r="J26" t="n">
-        <v>4.499400000000001</v>
+        <v>4.9979</v>
       </c>
       <c r="K26" t="n">
-        <v>4.604200000000001</v>
+        <v>4.9254</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.1048999999999993</v>
+        <v>0.07240000000000041</v>
       </c>
       <c r="M26" t="n">
-        <v>-11.8683</v>
+        <v>-12.3699</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.7009</v>
+        <v>-0.9744000000000002</v>
       </c>
       <c r="O26" t="n">
-        <v>-11.1674</v>
+        <v>-11.3952</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.0244</v>
+        <v>-1.0121</v>
       </c>
       <c r="Q26" t="n">
-        <v>-11.2666</v>
+        <v>-11.1349</v>
       </c>
       <c r="R26" t="n">
-        <v>10.2423</v>
+        <v>10.1227</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.0243</v>
+        <v>0.3718</v>
       </c>
       <c r="T26" t="n">
-        <v>1.2817</v>
+        <v>1.4169</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.305800000000001</v>
+        <v>-1.045</v>
       </c>
       <c r="V26" t="n">
-        <v>-2.0129</v>
+        <v>-2.0364</v>
       </c>
       <c r="W26" t="n">
-        <v>9.746300000000002</v>
+        <v>9.901400000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>-11.7594</v>
+        <v>-11.9377</v>
       </c>
     </row>
   </sheetData>
